--- a/schedule/fixtures/example_week.xlsx
+++ b/schedule/fixtures/example_week.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Микроэкономика (лекц.) доц. Холбаева С.</t>
+          <t>Микроэкономика (лекц.) доц. Соколова С.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -522,7 +522,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Физическая культура (практ.зан.) PhD Разуваева И.Ю.</t>
+          <t>Физическая культура (практ.зан.) PhD Рощина И.Ю.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>История экономических учений (на английском языке) (лекц.) проф. Карабаева Г.Ш.</t>
+          <t>История экономических учений (на английском языке) (лекц.) проф. Крылова Г.Ш.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Информационные технологии (лабр.) ст. преп. АртиковаЗ.З.</t>
+          <t>Информационные технологии (лабр.) ст. преп. АрхиповаЗ.З.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Планирование и прогнозирование в экономике (практ.зан.) доц. Эгамова М.Э.</t>
+          <t>Планирование и прогнозирование в экономике (практ.зан.) доц. Ершова М.Э.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Кураторский час Карабаева Г.Ш.</t>
+          <t>Кураторский час Крылова Г.Ш.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -629,7 +629,7 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>Гражданское право  (лпракт.зан)
-доц. Архангельская Е.Г.</t>
+доц. Афанасьева Е.Г.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Экология и природопользование (лекц.) доц. Рахимова Н.Э.</t>
+          <t>Экология и природопользование (лекц.) доц. Романова Н.Э.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Логистика (практ.зан.) ст. преп. Аюбов У.Т.</t>
+          <t>Логистика (практ.зан.) ст. преп. Аксенов У.Т.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Маркетинг (лекц.) доц. Юсупова Д.А.</t>
+          <t>Маркетинг (лекц.) доц. Юдина Д.А.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -710,7 +710,7 @@
       <c r="H12" t="inlineStr">
         <is>
           <t xml:space="preserve">Бизнес-планирование и прогнозирование деятельности предприятий ресторанного бизнеса (лекц.) 
-ст. ст. преп. Гулямова А.Н. </t>
+ст. ст. преп. Гаврилова А.Н. </t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Налоги и налогообложение (практ.зан..) доц. Ибраева С.А.</t>
+          <t>Налоги и налогообложение (практ.зан..) доц. Ильина С.А.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
